--- a/School-Data-Mapping-App/近隣中学校.xlsx
+++ b/School-Data-Mapping-App/近隣中学校.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\setou\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ysetou-hp\homepage\School-Data-Mapping-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983B1E76-4F4C-45F4-8348-662079040088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDB58DD-7C45-4D82-9071-4EA7CB36E1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4824" yWindow="3756" windowWidth="31824" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="3300" windowWidth="35760" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="school_data_geo" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="236">
   <si>
     <t>地区</t>
   </si>
@@ -730,6 +730,10 @@
   </si>
   <si>
     <t>愛媛県越智郡上島町弓削明神1-1</t>
+  </si>
+  <si>
+    <t>PR</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1092,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U107"/>
+  <dimension ref="A1:V107"/>
   <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="13.5" style="1" customWidth="1"/>
@@ -1100,7 +1104,7 @@
     <col min="3" max="3" width="34.5" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1117,55 +1121,58 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1181,12 +1188,9 @@
       <c r="E2">
         <v>133.22804300000001</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>159</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
       <c r="H2">
         <v>1</v>
       </c>
@@ -1194,22 +1198,22 @@
         <v>1</v>
       </c>
       <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
         <v>3</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <v>1</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1218,19 +1222,22 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
         <v>2</v>
       </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
       <c r="U2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1246,42 +1253,39 @@
       <c r="E3">
         <v>133.20347599999999</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>110</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
       <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>4</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>2</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>3</v>
       </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
       <c r="R3">
         <v>1</v>
       </c>
@@ -1292,10 +1296,13 @@
         <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1311,12 +1318,9 @@
       <c r="E4">
         <v>133.19079600000001</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>124</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
       <c r="H4">
         <v>0</v>
       </c>
@@ -1330,16 +1334,16 @@
         <v>0</v>
       </c>
       <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>2</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
       <c r="N4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1351,16 +1355,19 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1376,14 +1383,11 @@
       <c r="E5">
         <v>133.19392400000001</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>99</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1392,40 +1396,43 @@
         <v>0</v>
       </c>
       <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
         <v>2</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
       <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>4</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
       <c r="O5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
         <v>4</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>2</v>
       </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
         <v>3</v>
       </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1441,12 +1448,9 @@
       <c r="E6">
         <v>133.183243</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>80</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
       <c r="H6">
         <v>0</v>
       </c>
@@ -1463,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
@@ -1472,25 +1476,28 @@
         <v>1</v>
       </c>
       <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
         <v>2</v>
       </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="U6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1506,12 +1513,9 @@
       <c r="E7">
         <v>133.17770400000001</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>64</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
       <c r="H7">
         <v>0</v>
       </c>
@@ -1525,11 +1529,11 @@
         <v>0</v>
       </c>
       <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
         <v>2</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
       <c r="N7">
         <v>0</v>
       </c>
@@ -1546,16 +1550,19 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1571,12 +1578,9 @@
       <c r="E8">
         <v>133.221237</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>56</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
       <c r="H8">
         <v>0</v>
       </c>
@@ -1593,34 +1597,37 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
         <v>2</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>1</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1636,17 +1643,14 @@
       <c r="E9">
         <v>133.17970299999999</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>57</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1655,37 +1659,40 @@
         <v>0</v>
       </c>
       <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
         <v>3</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
       <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
         <v>6</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>3</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
       <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
         <v>3</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>8</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
       <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
         <v>3</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1701,12 +1708,9 @@
       <c r="E10">
         <v>133.10086100000001</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>53</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
       <c r="H10">
         <v>0</v>
       </c>
@@ -1717,40 +1721,43 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
         <v>2</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
       <c r="N10">
         <v>0</v>
       </c>
       <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>3</v>
       </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
       <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
         <v>3</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>5</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>4</v>
       </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
       <c r="U10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1766,12 +1773,9 @@
       <c r="E11">
         <v>133.174103</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>49</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
       <c r="H11">
         <v>0</v>
       </c>
@@ -1779,43 +1783,46 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>2</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q11">
         <v>2</v>
       </c>
       <c r="R11">
+        <v>2</v>
+      </c>
+      <c r="S11">
         <v>4</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>2</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>6</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1831,12 +1838,9 @@
       <c r="E12">
         <v>133.139297</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>35</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
       <c r="H12">
         <v>0</v>
       </c>
@@ -1853,19 +1857,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1879,8 +1883,11 @@
       <c r="U12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1896,20 +1903,17 @@
       <c r="E13">
         <v>133.16416899999999</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>25</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1944,8 +1948,11 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1961,17 +1968,14 @@
       <c r="E14">
         <v>133.27006499999999</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>16</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1980,10 +1984,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2009,8 +2013,11 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2026,12 +2033,9 @@
       <c r="E15">
         <v>133.142426</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>3</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
       <c r="H15">
         <v>0</v>
       </c>
@@ -2054,10 +2058,10 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2066,16 +2070,19 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2091,9 +2098,6 @@
       <c r="E16">
         <v>133.26918000000001</v>
       </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2139,8 +2143,11 @@
       <c r="U16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -2157,11 +2164,11 @@
         <v>133.36773700000001</v>
       </c>
       <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
         <v>225</v>
       </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
       <c r="H17">
         <v>0</v>
       </c>
@@ -2175,22 +2182,22 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -2204,8 +2211,11 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>52</v>
       </c>
@@ -2222,17 +2232,17 @@
         <v>133.35771199999999</v>
       </c>
       <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
         <v>213</v>
       </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>2</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
       <c r="J18">
         <v>0</v>
       </c>
@@ -2240,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -2269,8 +2279,11 @@
       <c r="U18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -2287,28 +2300,28 @@
         <v>133.36132799999999</v>
       </c>
       <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
         <v>213</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>2</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -2332,10 +2345,13 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -2352,13 +2368,13 @@
         <v>133.39746099999999</v>
       </c>
       <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20">
         <v>173</v>
       </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2370,37 +2386,40 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2417,11 +2436,11 @@
         <v>133.384491</v>
       </c>
       <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
         <v>187</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
       <c r="H21">
         <v>0</v>
       </c>
@@ -2444,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -2464,8 +2483,11 @@
       <c r="U21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2482,13 +2504,13 @@
         <v>133.32960499999999</v>
       </c>
       <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22">
         <v>161</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2503,10 +2525,10 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2529,8 +2551,11 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2547,11 +2572,11 @@
         <v>133.26885999999999</v>
       </c>
       <c r="F23">
+        <v>3</v>
+      </c>
+      <c r="G23">
         <v>140</v>
       </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
       <c r="H23">
         <v>0</v>
       </c>
@@ -2594,8 +2619,11 @@
       <c r="U23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -2612,11 +2640,11 @@
         <v>133.378052</v>
       </c>
       <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24">
         <v>140</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
       <c r="H24">
         <v>0</v>
       </c>
@@ -2627,16 +2655,16 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -2648,19 +2676,22 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2677,11 +2708,11 @@
         <v>133.43853799999999</v>
       </c>
       <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25">
         <v>149</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
       <c r="H25">
         <v>0</v>
       </c>
@@ -2701,11 +2732,11 @@
         <v>0</v>
       </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>2</v>
       </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
       <c r="P25">
         <v>0</v>
       </c>
@@ -2724,8 +2755,11 @@
       <c r="U25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>52</v>
       </c>
@@ -2741,14 +2775,11 @@
       <c r="E26">
         <v>133.28733800000001</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>146</v>
       </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2789,8 +2820,11 @@
       <c r="U26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -2806,17 +2840,14 @@
       <c r="E27">
         <v>133.396378</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>129</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
       <c r="H27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -2825,13 +2856,13 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>4</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -2840,22 +2871,25 @@
         <v>0</v>
       </c>
       <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>2</v>
       </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
       <c r="S27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -2871,12 +2905,9 @@
       <c r="E28">
         <v>133.381607</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>128</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
       <c r="H28">
         <v>0</v>
       </c>
@@ -2890,37 +2921,40 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
         <v>2</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -2936,12 +2970,9 @@
       <c r="E29">
         <v>133.30139199999999</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>117</v>
       </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
       <c r="H29">
         <v>0</v>
       </c>
@@ -2984,8 +3015,11 @@
       <c r="U29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -3001,26 +3035,23 @@
       <c r="E30">
         <v>133.271851</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>122</v>
       </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
       <c r="H30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -3038,19 +3069,22 @@
         <v>0</v>
       </c>
       <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>2</v>
       </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
       <c r="T30">
         <v>0</v>
       </c>
       <c r="U30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>52</v>
       </c>
@@ -3066,12 +3100,9 @@
       <c r="E31">
         <v>133.43351699999999</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>117</v>
       </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
       <c r="H31">
         <v>0</v>
       </c>
@@ -3094,11 +3125,11 @@
         <v>0</v>
       </c>
       <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>2</v>
       </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
       <c r="Q31">
         <v>0</v>
       </c>
@@ -3112,10 +3143,13 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>52</v>
       </c>
@@ -3131,17 +3165,14 @@
       <c r="E32">
         <v>133.36541700000001</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>130</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
       <c r="H32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
         <v>0</v>
@@ -3159,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -3179,8 +3210,11 @@
       <c r="U32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -3196,12 +3230,9 @@
       <c r="E33">
         <v>133.321945</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>106</v>
       </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
       <c r="H33">
         <v>0</v>
       </c>
@@ -3215,11 +3246,11 @@
         <v>0</v>
       </c>
       <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
         <v>2</v>
       </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
       <c r="N33">
         <v>0</v>
       </c>
@@ -3230,22 +3261,25 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="T33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>52</v>
       </c>
@@ -3261,12 +3295,9 @@
       <c r="E34">
         <v>133.412003</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>112</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
       <c r="H34">
         <v>0</v>
       </c>
@@ -3295,10 +3326,10 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -3307,10 +3338,13 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -3326,12 +3360,9 @@
       <c r="E35">
         <v>133.247803</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>101</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
       <c r="H35">
         <v>0</v>
       </c>
@@ -3339,43 +3370,46 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
         <v>2</v>
       </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
       <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
         <v>2</v>
       </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
       <c r="S35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -3391,14 +3425,11 @@
       <c r="E36">
         <v>133.37970000000001</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>81</v>
       </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -3419,16 +3450,16 @@
         <v>0</v>
       </c>
       <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
         <v>2</v>
       </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
       <c r="Q36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -3439,8 +3470,11 @@
       <c r="U36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>52</v>
       </c>
@@ -3456,20 +3490,17 @@
       <c r="E37">
         <v>133.42816199999999</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>95</v>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -3490,22 +3521,25 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
       <c r="U37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>52</v>
       </c>
@@ -3521,12 +3555,9 @@
       <c r="E38">
         <v>133.342499</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>91</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
       <c r="H38">
         <v>0</v>
       </c>
@@ -3546,10 +3577,10 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -3569,8 +3600,11 @@
       <c r="U38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>52</v>
       </c>
@@ -3586,23 +3620,20 @@
       <c r="E39">
         <v>133.36120600000001</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>71</v>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3611,10 +3642,10 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39">
         <v>0</v>
@@ -3634,8 +3665,11 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -3651,12 +3685,9 @@
       <c r="E40">
         <v>133.40365600000001</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>98</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
         <v>0</v>
       </c>
@@ -3691,16 +3722,19 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="U40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -3716,17 +3750,14 @@
       <c r="E41">
         <v>133.32753</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>72</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3764,8 +3795,11 @@
       <c r="U41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -3781,12 +3815,9 @@
       <c r="E42">
         <v>133.414276</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>78</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
       <c r="H42">
         <v>0</v>
       </c>
@@ -3809,11 +3840,11 @@
         <v>0</v>
       </c>
       <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
         <v>2</v>
       </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
       <c r="Q42">
         <v>0</v>
       </c>
@@ -3829,8 +3860,11 @@
       <c r="U42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>52</v>
       </c>
@@ -3846,32 +3880,29 @@
       <c r="E43">
         <v>133.320663</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>67</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
       <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
         <v>2</v>
       </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43">
         <v>1</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -3883,10 +3914,10 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43">
         <v>0</v>
@@ -3894,8 +3925,11 @@
       <c r="U43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -3911,12 +3945,9 @@
       <c r="E44">
         <v>133.27827500000001</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>39</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
       <c r="H44">
         <v>0</v>
       </c>
@@ -3959,8 +3990,11 @@
       <c r="U44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -3976,17 +4010,14 @@
       <c r="E45">
         <v>133.28431699999999</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>32</v>
       </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
       <c r="H45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -4001,16 +4032,16 @@
         <v>0</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -4024,8 +4055,11 @@
       <c r="U45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>52</v>
       </c>
@@ -4041,12 +4075,9 @@
       <c r="E46">
         <v>133.31471300000001</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>27</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
       <c r="H46">
         <v>0</v>
       </c>
@@ -4087,10 +4118,13 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -4106,17 +4140,14 @@
       <c r="E47">
         <v>133.375473</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>24</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
       <c r="H47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -4146,16 +4177,19 @@
         <v>0</v>
       </c>
       <c r="S47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>52</v>
       </c>
@@ -4171,12 +4205,9 @@
       <c r="E48">
         <v>133.34272799999999</v>
       </c>
-      <c r="F48">
+      <c r="G48">
         <v>12</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
       <c r="H48">
         <v>0</v>
       </c>
@@ -4219,8 +4250,11 @@
       <c r="U48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -4236,20 +4270,17 @@
       <c r="E49">
         <v>133.072723</v>
       </c>
-      <c r="F49">
+      <c r="G49">
         <v>159</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -4258,7 +4289,7 @@
         <v>1</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -4284,8 +4315,11 @@
       <c r="U49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>117</v>
       </c>
@@ -4301,20 +4335,17 @@
       <c r="E50">
         <v>133.09635900000001</v>
       </c>
-      <c r="F50">
+      <c r="G50">
         <v>119</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
       <c r="H50">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -4323,22 +4354,22 @@
         <v>0</v>
       </c>
       <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
         <v>2</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>1</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -4349,8 +4380,11 @@
       <c r="U50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -4366,12 +4400,9 @@
       <c r="E51">
         <v>133.02359000000001</v>
       </c>
-      <c r="F51">
+      <c r="G51">
         <v>96</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
       <c r="H51">
         <v>0</v>
       </c>
@@ -4388,10 +4419,10 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -4414,8 +4445,11 @@
       <c r="U51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>117</v>
       </c>
@@ -4431,20 +4465,17 @@
       <c r="E52">
         <v>133.05744899999999</v>
       </c>
-      <c r="F52">
+      <c r="G52">
         <v>95</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -4474,13 +4505,16 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -4496,14 +4530,11 @@
       <c r="E53">
         <v>132.96839900000001</v>
       </c>
-      <c r="F53">
+      <c r="G53">
         <v>92</v>
       </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
       <c r="H53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -4521,10 +4552,10 @@
         <v>0</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -4544,8 +4575,11 @@
       <c r="U53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -4561,12 +4595,9 @@
       <c r="E54">
         <v>132.91091900000001</v>
       </c>
-      <c r="F54">
+      <c r="G54">
         <v>30</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
       <c r="H54">
         <v>0</v>
       </c>
@@ -4609,8 +4640,11 @@
       <c r="U54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>117</v>
       </c>
@@ -4626,12 +4660,9 @@
       <c r="E55">
         <v>133.046967</v>
       </c>
-      <c r="F55">
+      <c r="G55">
         <v>28</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
       <c r="H55">
         <v>0</v>
       </c>
@@ -4674,8 +4705,11 @@
       <c r="U55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -4691,12 +4725,9 @@
       <c r="E56">
         <v>133.10870399999999</v>
       </c>
-      <c r="F56">
+      <c r="G56">
         <v>25</v>
       </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
       <c r="H56">
         <v>0</v>
       </c>
@@ -4710,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -4739,8 +4770,11 @@
       <c r="U56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -4756,12 +4790,9 @@
       <c r="E57">
         <v>133.03680399999999</v>
       </c>
-      <c r="F57">
+      <c r="G57">
         <v>19</v>
       </c>
-      <c r="G57">
-        <v>0</v>
-      </c>
       <c r="H57">
         <v>0</v>
       </c>
@@ -4804,8 +4835,11 @@
       <c r="U57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -4821,12 +4855,9 @@
       <c r="E58">
         <v>133.07884200000001</v>
       </c>
-      <c r="F58">
+      <c r="G58">
         <v>8</v>
       </c>
-      <c r="G58">
-        <v>0</v>
-      </c>
       <c r="H58">
         <v>0</v>
       </c>
@@ -4852,10 +4883,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -4869,8 +4900,11 @@
       <c r="U58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -4886,14 +4920,11 @@
       <c r="E59">
         <v>133.08604399999999</v>
       </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
       <c r="H59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4917,22 +4948,25 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59">
         <v>1</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
         <v>2</v>
       </c>
-      <c r="U59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>117</v>
       </c>
@@ -4948,9 +4982,6 @@
       <c r="E60">
         <v>133.135132</v>
       </c>
-      <c r="G60">
-        <v>0</v>
-      </c>
       <c r="H60">
         <v>0</v>
       </c>
@@ -4993,8 +5024,11 @@
       <c r="U60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>142</v>
       </c>
@@ -5010,12 +5044,9 @@
       <c r="E61">
         <v>132.80175800000001</v>
       </c>
-      <c r="F61">
+      <c r="G61">
         <v>252</v>
       </c>
-      <c r="G61">
-        <v>0</v>
-      </c>
       <c r="H61">
         <v>0</v>
       </c>
@@ -5058,8 +5089,11 @@
       <c r="U61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>142</v>
       </c>
@@ -5075,12 +5109,9 @@
       <c r="E62">
         <v>132.74648999999999</v>
       </c>
-      <c r="F62">
+      <c r="G62">
         <v>244</v>
       </c>
-      <c r="G62">
-        <v>0</v>
-      </c>
       <c r="H62">
         <v>0</v>
       </c>
@@ -5123,8 +5154,11 @@
       <c r="U62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>142</v>
       </c>
@@ -5140,12 +5174,9 @@
       <c r="E63">
         <v>132.776184</v>
       </c>
-      <c r="F63">
+      <c r="G63">
         <v>223</v>
       </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
       <c r="H63">
         <v>0</v>
       </c>
@@ -5156,19 +5187,19 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63">
         <v>1</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -5188,8 +5219,11 @@
       <c r="U63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>142</v>
       </c>
@@ -5205,12 +5239,9 @@
       <c r="E64">
         <v>132.793564</v>
       </c>
-      <c r="F64">
+      <c r="G64">
         <v>231</v>
       </c>
-      <c r="G64">
-        <v>0</v>
-      </c>
       <c r="H64">
         <v>0</v>
       </c>
@@ -5253,8 +5284,11 @@
       <c r="U64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>142</v>
       </c>
@@ -5270,12 +5304,9 @@
       <c r="E65">
         <v>132.72036700000001</v>
       </c>
-      <c r="F65">
+      <c r="G65">
         <v>210</v>
       </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
       <c r="H65">
         <v>0</v>
       </c>
@@ -5283,10 +5314,10 @@
         <v>0</v>
       </c>
       <c r="J65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -5318,8 +5349,11 @@
       <c r="U65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>142</v>
       </c>
@@ -5335,14 +5369,11 @@
       <c r="E66">
         <v>132.76409899999999</v>
       </c>
-      <c r="F66">
+      <c r="G66">
         <v>209</v>
       </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -5351,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -5383,8 +5414,11 @@
       <c r="U66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>142</v>
       </c>
@@ -5400,12 +5434,9 @@
       <c r="E67">
         <v>132.806366</v>
       </c>
-      <c r="F67">
+      <c r="G67">
         <v>177</v>
       </c>
-      <c r="G67">
-        <v>0</v>
-      </c>
       <c r="H67">
         <v>0</v>
       </c>
@@ -5448,8 +5479,11 @@
       <c r="U67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -5465,12 +5499,9 @@
       <c r="E68">
         <v>132.71878100000001</v>
       </c>
-      <c r="F68">
+      <c r="G68">
         <v>187</v>
       </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
       <c r="H68">
         <v>0</v>
       </c>
@@ -5513,8 +5544,11 @@
       <c r="U68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>142</v>
       </c>
@@ -5530,12 +5564,9 @@
       <c r="E69">
         <v>132.749741</v>
       </c>
-      <c r="F69">
+      <c r="G69">
         <v>187</v>
       </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
       <c r="H69">
         <v>0</v>
       </c>
@@ -5578,8 +5609,11 @@
       <c r="U69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>142</v>
       </c>
@@ -5595,12 +5629,9 @@
       <c r="E70">
         <v>132.74067700000001</v>
       </c>
-      <c r="F70">
+      <c r="G70">
         <v>186</v>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
       <c r="H70">
         <v>0</v>
       </c>
@@ -5629,22 +5660,25 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>142</v>
       </c>
@@ -5660,12 +5694,9 @@
       <c r="E71">
         <v>132.78956600000001</v>
       </c>
-      <c r="F71">
+      <c r="G71">
         <v>177</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
       <c r="H71">
         <v>0</v>
       </c>
@@ -5682,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5694,10 +5725,10 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -5708,8 +5739,11 @@
       <c r="U71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>142</v>
       </c>
@@ -5725,12 +5759,9 @@
       <c r="E72">
         <v>132.753693</v>
       </c>
-      <c r="F72">
+      <c r="G72">
         <v>163</v>
       </c>
-      <c r="G72">
-        <v>0</v>
-      </c>
       <c r="H72">
         <v>0</v>
       </c>
@@ -5744,10 +5775,10 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -5759,11 +5790,11 @@
         <v>0</v>
       </c>
       <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
         <v>2</v>
       </c>
-      <c r="R72">
-        <v>0</v>
-      </c>
       <c r="S72">
         <v>0</v>
       </c>
@@ -5773,8 +5804,11 @@
       <c r="U72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>142</v>
       </c>
@@ -5790,12 +5824,9 @@
       <c r="E73">
         <v>132.74972500000001</v>
       </c>
-      <c r="F73">
+      <c r="G73">
         <v>153</v>
       </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
       <c r="H73">
         <v>0</v>
       </c>
@@ -5803,10 +5834,10 @@
         <v>0</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -5838,8 +5869,11 @@
       <c r="U73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>142</v>
       </c>
@@ -5855,12 +5889,9 @@
       <c r="E74">
         <v>132.836838</v>
       </c>
-      <c r="F74">
+      <c r="G74">
         <v>138</v>
       </c>
-      <c r="G74">
-        <v>0</v>
-      </c>
       <c r="H74">
         <v>0</v>
       </c>
@@ -5903,8 +5934,11 @@
       <c r="U74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>142</v>
       </c>
@@ -5920,12 +5954,9 @@
       <c r="E75">
         <v>132.72363300000001</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>128</v>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
       <c r="H75">
         <v>0</v>
       </c>
@@ -5933,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -5968,8 +5999,11 @@
       <c r="U75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>142</v>
       </c>
@@ -5985,14 +6019,11 @@
       <c r="E76">
         <v>132.74880999999999</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>140</v>
       </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -6001,10 +6032,10 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -6019,10 +6050,10 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -6033,8 +6064,11 @@
       <c r="U76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>142</v>
       </c>
@@ -6050,14 +6084,11 @@
       <c r="E77">
         <v>132.73481799999999</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>130</v>
       </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
       <c r="H77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -6098,8 +6129,11 @@
       <c r="U77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>142</v>
       </c>
@@ -6115,12 +6149,9 @@
       <c r="E78">
         <v>132.70120199999999</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>125</v>
       </c>
-      <c r="G78">
-        <v>0</v>
-      </c>
       <c r="H78">
         <v>0</v>
       </c>
@@ -6163,8 +6194,11 @@
       <c r="U78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>142</v>
       </c>
@@ -6180,12 +6214,9 @@
       <c r="E79">
         <v>132.78367600000001</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>124</v>
       </c>
-      <c r="G79">
-        <v>0</v>
-      </c>
       <c r="H79">
         <v>0</v>
       </c>
@@ -6228,8 +6259,11 @@
       <c r="U79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>142</v>
       </c>
@@ -6245,21 +6279,18 @@
       <c r="E80">
         <v>132.77784700000001</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>90</v>
       </c>
-      <c r="G80">
-        <v>0</v>
-      </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
         <v>2</v>
       </c>
-      <c r="J80">
-        <v>0</v>
-      </c>
       <c r="K80">
         <v>0</v>
       </c>
@@ -6293,8 +6324,11 @@
       <c r="U80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>142</v>
       </c>
@@ -6310,12 +6344,9 @@
       <c r="E81">
         <v>132.78175400000001</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>86</v>
       </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
       <c r="H81">
         <v>0</v>
       </c>
@@ -6358,8 +6389,11 @@
       <c r="U81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>142</v>
       </c>
@@ -6375,12 +6409,9 @@
       <c r="E82">
         <v>132.77439899999999</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>96</v>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
       <c r="H82">
         <v>0</v>
       </c>
@@ -6409,10 +6440,10 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -6423,8 +6454,11 @@
       <c r="U82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>142</v>
       </c>
@@ -6440,12 +6474,9 @@
       <c r="E83">
         <v>132.81843599999999</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>91</v>
       </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
       <c r="H83">
         <v>0</v>
       </c>
@@ -6465,10 +6496,10 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83">
         <v>0</v>
@@ -6488,8 +6519,11 @@
       <c r="U83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>142</v>
       </c>
@@ -6505,12 +6539,9 @@
       <c r="E84">
         <v>132.802322</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>60</v>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
       <c r="H84">
         <v>0</v>
       </c>
@@ -6553,8 +6584,11 @@
       <c r="U84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>142</v>
       </c>
@@ -6570,12 +6604,9 @@
       <c r="E85">
         <v>132.80735799999999</v>
       </c>
-      <c r="F85">
+      <c r="G85">
         <v>60</v>
       </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
       <c r="H85">
         <v>0</v>
       </c>
@@ -6583,10 +6614,10 @@
         <v>0</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -6618,8 +6649,11 @@
       <c r="U85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>142</v>
       </c>
@@ -6635,12 +6669,9 @@
       <c r="E86">
         <v>132.70890800000001</v>
       </c>
-      <c r="F86">
+      <c r="G86">
         <v>41</v>
       </c>
-      <c r="G86">
-        <v>0</v>
-      </c>
       <c r="H86">
         <v>0</v>
       </c>
@@ -6683,8 +6714,11 @@
       <c r="U86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>142</v>
       </c>
@@ -6700,12 +6734,9 @@
       <c r="E87">
         <v>132.624619</v>
       </c>
-      <c r="F87">
+      <c r="G87">
         <v>14</v>
       </c>
-      <c r="G87">
-        <v>0</v>
-      </c>
       <c r="H87">
         <v>0</v>
       </c>
@@ -6748,8 +6779,11 @@
       <c r="U87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>142</v>
       </c>
@@ -6765,12 +6799,9 @@
       <c r="E88">
         <v>132.66973899999999</v>
       </c>
-      <c r="F88">
+      <c r="G88">
         <v>7</v>
       </c>
-      <c r="G88">
-        <v>0</v>
-      </c>
       <c r="H88">
         <v>0</v>
       </c>
@@ -6813,8 +6844,11 @@
       <c r="U88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>142</v>
       </c>
@@ -6830,12 +6864,9 @@
       <c r="E89">
         <v>132.87202500000001</v>
       </c>
-      <c r="F89">
+      <c r="G89">
         <v>5</v>
       </c>
-      <c r="G89">
-        <v>0</v>
-      </c>
       <c r="H89">
         <v>0</v>
       </c>
@@ -6870,16 +6901,19 @@
         <v>0</v>
       </c>
       <c r="S89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>199</v>
       </c>
@@ -6895,56 +6929,56 @@
       <c r="E90">
         <v>132.977158</v>
       </c>
-      <c r="F90">
+      <c r="G90">
         <v>198</v>
       </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
       <c r="H90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90">
         <v>1</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90">
         <v>0</v>
       </c>
       <c r="L90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90">
         <v>0</v>
       </c>
       <c r="O90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
         <v>2</v>
       </c>
-      <c r="T90">
-        <v>1</v>
-      </c>
       <c r="U90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>199</v>
       </c>
@@ -6960,56 +6994,56 @@
       <c r="E91">
         <v>133.001328</v>
       </c>
-      <c r="F91">
+      <c r="G91">
         <v>154</v>
       </c>
-      <c r="G91">
-        <v>0</v>
-      </c>
       <c r="H91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91">
         <v>1</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91">
         <v>0</v>
       </c>
       <c r="L91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
         <v>2</v>
       </c>
-      <c r="O91">
+      <c r="P91">
         <v>3</v>
       </c>
-      <c r="P91">
+      <c r="Q91">
         <v>2</v>
       </c>
-      <c r="Q91">
-        <v>1</v>
-      </c>
       <c r="R91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91">
         <v>0</v>
       </c>
       <c r="T91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>199</v>
       </c>
@@ -7025,39 +7059,36 @@
       <c r="E92">
         <v>132.99290500000001</v>
       </c>
-      <c r="F92">
+      <c r="G92">
         <v>152</v>
       </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
       <c r="H92">
         <v>1</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92">
         <v>1</v>
       </c>
       <c r="O92">
+        <v>1</v>
+      </c>
+      <c r="P92">
         <v>3</v>
       </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
       <c r="Q92">
         <v>0</v>
       </c>
@@ -7065,16 +7096,19 @@
         <v>0</v>
       </c>
       <c r="S92">
+        <v>0</v>
+      </c>
+      <c r="T92">
         <v>2</v>
       </c>
-      <c r="T92">
-        <v>0</v>
-      </c>
       <c r="U92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>199</v>
       </c>
@@ -7090,20 +7124,17 @@
       <c r="E93">
         <v>132.998062</v>
       </c>
-      <c r="F93">
+      <c r="G93">
         <v>139</v>
       </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93">
         <v>0</v>
@@ -7115,7 +7146,7 @@
         <v>0</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93">
         <v>1</v>
@@ -7127,7 +7158,7 @@
         <v>1</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S93">
         <v>0</v>
@@ -7138,8 +7169,11 @@
       <c r="U93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>199</v>
       </c>
@@ -7155,35 +7189,32 @@
       <c r="E94">
         <v>132.95782500000001</v>
       </c>
-      <c r="F94">
+      <c r="G94">
         <v>95</v>
       </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94">
         <v>1</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94">
         <v>0</v>
@@ -7198,13 +7229,16 @@
         <v>0</v>
       </c>
       <c r="T94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>199</v>
       </c>
@@ -7220,14 +7254,11 @@
       <c r="E95">
         <v>133.032883</v>
       </c>
-      <c r="F95">
+      <c r="G95">
         <v>86</v>
       </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
       <c r="H95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -7236,13 +7267,13 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95">
         <v>1</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95">
         <v>0</v>
@@ -7266,10 +7297,13 @@
         <v>0</v>
       </c>
       <c r="U95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>199</v>
       </c>
@@ -7285,12 +7319,9 @@
       <c r="E96">
         <v>132.98088100000001</v>
       </c>
-      <c r="F96">
+      <c r="G96">
         <v>60</v>
       </c>
-      <c r="G96">
-        <v>0</v>
-      </c>
       <c r="H96">
         <v>0</v>
       </c>
@@ -7310,10 +7341,10 @@
         <v>0</v>
       </c>
       <c r="N96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -7322,19 +7353,22 @@
         <v>0</v>
       </c>
       <c r="R96">
+        <v>0</v>
+      </c>
+      <c r="S96">
         <v>2</v>
       </c>
-      <c r="S96">
-        <v>0</v>
-      </c>
       <c r="T96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -7350,17 +7384,14 @@
       <c r="E97">
         <v>132.92652899999999</v>
       </c>
-      <c r="F97">
+      <c r="G97">
         <v>60</v>
       </c>
-      <c r="G97">
-        <v>0</v>
-      </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -7396,10 +7427,13 @@
         <v>0</v>
       </c>
       <c r="U97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>199</v>
       </c>
@@ -7415,12 +7449,9 @@
       <c r="E98">
         <v>133.11183199999999</v>
       </c>
-      <c r="F98">
+      <c r="G98">
         <v>36</v>
       </c>
-      <c r="G98">
-        <v>0</v>
-      </c>
       <c r="H98">
         <v>0</v>
       </c>
@@ -7431,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98">
         <v>1</v>
@@ -7440,31 +7471,34 @@
         <v>1</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98">
         <v>0</v>
       </c>
       <c r="R98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S98">
+        <v>1</v>
+      </c>
+      <c r="T98">
         <v>3</v>
       </c>
-      <c r="T98">
-        <v>1</v>
-      </c>
       <c r="U98">
+        <v>1</v>
+      </c>
+      <c r="V98">
         <v>3</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>199</v>
       </c>
@@ -7480,12 +7514,9 @@
       <c r="E99">
         <v>132.94154399999999</v>
       </c>
-      <c r="F99">
+      <c r="G99">
         <v>32</v>
       </c>
-      <c r="G99">
-        <v>0</v>
-      </c>
       <c r="H99">
         <v>0</v>
       </c>
@@ -7528,8 +7559,11 @@
       <c r="U99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>199</v>
       </c>
@@ -7545,12 +7579,9 @@
       <c r="E100">
         <v>133.01693700000001</v>
       </c>
-      <c r="F100">
+      <c r="G100">
         <v>23</v>
       </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
       <c r="H100">
         <v>0</v>
       </c>
@@ -7593,8 +7624,11 @@
       <c r="U100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>199</v>
       </c>
@@ -7610,17 +7644,14 @@
       <c r="E101">
         <v>133.03980999999999</v>
       </c>
-      <c r="F101">
+      <c r="G101">
         <v>21</v>
       </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
       <c r="H101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -7641,10 +7672,10 @@
         <v>0</v>
       </c>
       <c r="P101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101">
         <v>0</v>
@@ -7656,10 +7687,13 @@
         <v>0</v>
       </c>
       <c r="U101">
+        <v>0</v>
+      </c>
+      <c r="V101">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>199</v>
       </c>
@@ -7675,12 +7709,9 @@
       <c r="E102">
         <v>133.032104</v>
       </c>
-      <c r="F102">
+      <c r="G102">
         <v>22</v>
       </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
       <c r="H102">
         <v>0</v>
       </c>
@@ -7712,19 +7743,22 @@
         <v>0</v>
       </c>
       <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
         <v>2</v>
       </c>
-      <c r="S102">
-        <v>1</v>
-      </c>
       <c r="T102">
         <v>1</v>
       </c>
       <c r="U102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>199</v>
       </c>
@@ -7740,12 +7774,9 @@
       <c r="E103">
         <v>132.852631</v>
       </c>
-      <c r="F103">
+      <c r="G103">
         <v>15</v>
       </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
       <c r="H103">
         <v>0</v>
       </c>
@@ -7788,8 +7819,11 @@
       <c r="U103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>199</v>
       </c>
@@ -7805,11 +7839,8 @@
       <c r="E104">
         <v>132.87725800000001</v>
       </c>
-      <c r="F104">
-        <v>1</v>
-      </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -7853,8 +7884,11 @@
       <c r="U104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>199</v>
       </c>
@@ -7871,7 +7905,7 @@
         <v>132.96644599999999</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>230</v>
       </c>
@@ -7887,26 +7921,23 @@
       <c r="E106">
         <v>133.14868200000001</v>
       </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
       <c r="H106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106">
         <v>1</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106">
         <v>0</v>
       </c>
       <c r="L106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N106">
         <v>0</v>
@@ -7921,19 +7952,22 @@
         <v>0</v>
       </c>
       <c r="R106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S106">
+        <v>1</v>
+      </c>
+      <c r="T106">
         <v>4</v>
       </c>
-      <c r="T106">
-        <v>0</v>
-      </c>
       <c r="U106">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+        <v>0</v>
+      </c>
+      <c r="V106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>230</v>
       </c>
@@ -7949,9 +7983,6 @@
       <c r="E107">
         <v>133.20405600000001</v>
       </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
       <c r="H107">
         <v>0</v>
       </c>
@@ -7965,13 +7996,13 @@
         <v>0</v>
       </c>
       <c r="L107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -7983,21 +8014,24 @@
         <v>0</v>
       </c>
       <c r="R107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S107">
+        <v>1</v>
+      </c>
+      <c r="T107">
         <v>4</v>
       </c>
-      <c r="T107">
-        <v>1</v>
-      </c>
       <c r="U107">
+        <v>1</v>
+      </c>
+      <c r="V107">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>